--- a/競輪AI_AI仕様書.xlsx
+++ b/競輪AI_AI仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\競輪AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A81FB38-5AFD-4B86-9345-EA0C12ACC2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF3153F-3883-4F81-809A-08FF32C11968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13850" windowHeight="10170" tabRatio="803" xr2:uid="{D86970A0-761E-4CC6-AE5F-2C47C14FC1F3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="803" xr2:uid="{D86970A0-761E-4CC6-AE5F-2C47C14FC1F3}"/>
   </bookViews>
   <sheets>
     <sheet name="00_元データ辞書" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="387">
   <si>
     <t>No</t>
   </si>
@@ -1331,6 +1331,22 @@
   </si>
   <si>
     <t>　　最終　08：00～14：00</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>当日データから取得できない為いったん除外</t>
+    <rPh sb="0" eb="2">
+      <t>トウジツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>タメ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジョガイ</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1391,12 +1407,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -1529,7 +1551,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1673,6 +1695,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3295,15 +3329,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DEDE6F1-F548-44AA-88A8-AFAF8591A66C}">
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="4.08203125" customWidth="1"/>
     <col min="2" max="3" width="22.58203125" customWidth="1"/>
     <col min="4" max="5" width="30.58203125" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3320,7 +3355,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -3337,7 +3372,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -3354,7 +3389,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -3371,7 +3406,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -3388,7 +3423,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -3405,96 +3440,98 @@
         <v>267</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5">
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>105</v>
+        <v>274</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>106</v>
+        <v>275</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5">
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="48"/>
+      <c r="B10" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>269</v>
+      </c>
+      <c r="E10" s="49" t="s">
+        <v>267</v>
+      </c>
+      <c r="F10" s="51" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="48"/>
+      <c r="B11" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C11" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D11" s="49" t="s">
         <v>273</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E11" s="50" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="5">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="5">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="7">
-        <v>10</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="13" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="14" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="15" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="16" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+      <c r="F11" s="51" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="13" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="14" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="15" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="16" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="17" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="18" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="19" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
